--- a/artfynd/A 50604-2023 artfynd.xlsx
+++ b/artfynd/A 50604-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50604-2023 artfynd.xlsx
+++ b/artfynd/A 50604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112909289</v>
+        <v>112912808</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426514</v>
+        <v>426390</v>
       </c>
       <c r="R2" t="n">
-        <v>6923242</v>
+        <v>6923874</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112909161</v>
+        <v>112908137</v>
       </c>
       <c r="B3" t="n">
-        <v>77777</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426498</v>
+        <v>426220</v>
       </c>
       <c r="R3" t="n">
-        <v>6923343</v>
+        <v>6923625</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112909555</v>
+        <v>112908641</v>
       </c>
       <c r="B4" t="n">
-        <v>56777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426514</v>
+        <v>426346</v>
       </c>
       <c r="R4" t="n">
-        <v>6923178</v>
+        <v>6923502</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112908773</v>
+        <v>112908674</v>
       </c>
       <c r="B5" t="n">
-        <v>79121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426430</v>
+        <v>426441</v>
       </c>
       <c r="R5" t="n">
-        <v>6923430</v>
+        <v>6923473</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1087,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112908756</v>
+        <v>112909161</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426430</v>
+        <v>426498</v>
       </c>
       <c r="R6" t="n">
-        <v>6923430</v>
+        <v>6923344</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112908937</v>
+        <v>112911802</v>
       </c>
       <c r="B7" t="n">
-        <v>97175</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426485</v>
+        <v>426662</v>
       </c>
       <c r="R7" t="n">
-        <v>6923407</v>
+        <v>6923509</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1267,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett trettiotal rosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112908641</v>
+        <v>112908024</v>
       </c>
       <c r="B8" t="n">
-        <v>77777</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426346</v>
+        <v>426240</v>
       </c>
       <c r="R8" t="n">
-        <v>6923502</v>
+        <v>6923577</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112912808</v>
+        <v>112908353</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,21 +1372,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426391</v>
+        <v>426266</v>
       </c>
       <c r="R9" t="n">
-        <v>6923874</v>
+        <v>6923556</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1504,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112908375</v>
+        <v>112908756</v>
       </c>
       <c r="B10" t="n">
-        <v>97175</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426260</v>
+        <v>426430</v>
       </c>
       <c r="R10" t="n">
-        <v>6923573</v>
+        <v>6923430</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1607,37 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112912030</v>
+        <v>112909289</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426508</v>
+        <v>426515</v>
       </c>
       <c r="R11" t="n">
-        <v>6923542</v>
+        <v>6923242</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1710,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112911802</v>
+        <v>112911104</v>
       </c>
       <c r="B12" t="n">
-        <v>77777</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426662</v>
+        <v>426831</v>
       </c>
       <c r="R12" t="n">
-        <v>6923509</v>
+        <v>6923152</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1813,37 +1753,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112912803</v>
+        <v>112907995</v>
       </c>
       <c r="B13" t="n">
-        <v>56756</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426391</v>
+        <v>426209</v>
       </c>
       <c r="R13" t="n">
-        <v>6923874</v>
+        <v>6923564</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1890,11 +1825,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Många ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,15 +1851,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112908335</v>
+        <v>112912030</v>
       </c>
       <c r="B14" t="n">
-        <v>56863</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,21 +1862,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426286</v>
+        <v>426508</v>
       </c>
       <c r="R14" t="n">
-        <v>6923548</v>
+        <v>6923542</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1998,11 +1923,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tre individer.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,37 +1949,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112909266</v>
+        <v>112908773</v>
       </c>
       <c r="B15" t="n">
-        <v>77002</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426517</v>
+        <v>426430</v>
       </c>
       <c r="R15" t="n">
-        <v>6923278</v>
+        <v>6923430</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2132,37 +2047,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112909369</v>
+        <v>112909266</v>
       </c>
       <c r="B16" t="n">
-        <v>97175</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426514</v>
+        <v>426517</v>
       </c>
       <c r="R16" t="n">
-        <v>6923178</v>
+        <v>6923278</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2235,15 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112909271</v>
+        <v>112912803</v>
       </c>
       <c r="B17" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426517</v>
+        <v>426390</v>
       </c>
       <c r="R17" t="n">
-        <v>6923278</v>
+        <v>6923874</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2312,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Många ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,37 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112908137</v>
+        <v>112909555</v>
       </c>
       <c r="B18" t="n">
-        <v>77777</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100110</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2379,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426220</v>
+        <v>426515</v>
       </c>
       <c r="R18" t="n">
-        <v>6923626</v>
+        <v>6923177</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2441,15 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112908353</v>
+        <v>112908335</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,21 +2357,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2482,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426265</v>
+        <v>426286</v>
       </c>
       <c r="R19" t="n">
-        <v>6923556</v>
+        <v>6923548</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2518,6 +2418,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tre individer.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,37 +2449,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112908674</v>
+        <v>112907947</v>
       </c>
       <c r="B20" t="n">
-        <v>77777</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426440</v>
+        <v>426166</v>
       </c>
       <c r="R20" t="n">
-        <v>6923472</v>
+        <v>6923557</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2647,37 +2547,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112907995</v>
+        <v>112908375</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426209</v>
+        <v>426260</v>
       </c>
       <c r="R21" t="n">
-        <v>6923565</v>
+        <v>6923574</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2750,37 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112908024</v>
+        <v>112908937</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2791,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426240</v>
+        <v>426486</v>
       </c>
       <c r="R22" t="n">
-        <v>6923577</v>
+        <v>6923407</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2827,6 +2717,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett trettiotal rosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2856,12 +2751,7 @@
         <v>112908957</v>
       </c>
       <c r="B23" t="n">
-        <v>97175</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2787,7 @@
         <v>426454</v>
       </c>
       <c r="R23" t="n">
-        <v>6923407</v>
+        <v>6923406</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2956,37 +2846,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112908672</v>
+        <v>112909369</v>
       </c>
       <c r="B24" t="n">
-        <v>77778</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2997,10 +2882,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426407</v>
+        <v>426515</v>
       </c>
       <c r="R24" t="n">
-        <v>6923483</v>
+        <v>6923177</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3059,15 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112911104</v>
+        <v>112908672</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,21 +2955,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3100,10 +2980,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426831</v>
+        <v>426407</v>
       </c>
       <c r="R25" t="n">
-        <v>6923152</v>
+        <v>6923483</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3159,6 +3039,104 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112909271</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hedningskällan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>426517</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6923278</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50604-2023 artfynd.xlsx
+++ b/artfynd/A 50604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912808</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908641</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112911802</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908353</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908756</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909289</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112911104</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112907995</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912030</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908773</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909266</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912803</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909555</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908335</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2544,6 +2639,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112907947</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908375</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908937</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2843,6 +2953,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908957</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2941,6 +3056,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909369</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3039,6 +3159,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112908672</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3137,8 +3262,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112909271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>